--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484543_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484543_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1244</v>
+        <v>5.482</v>
       </c>
       <c r="E2" t="n">
-        <v>6.355</v>
+        <v>5.4896</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2306</v>
+        <v>-0.0076</v>
       </c>
       <c r="G2" t="n">
         <v>1.3077</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0717</v>
+        <v>1.4293</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7564</v>
+        <v>0.891</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3153</v>
+        <v>0.5382</v>
       </c>
       <c r="V2" t="n">
         <v>1.4622</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2848</v>
+        <v>3.4638</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7049</v>
+        <v>2.7599</v>
       </c>
       <c r="F3" t="n">
-        <v>0.58</v>
+        <v>0.7038</v>
       </c>
       <c r="G3" t="n">
         <v>0.08309999999999999</v>
@@ -688,13 +688,13 @@
         <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4121</v>
+        <v>0.5911</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3092</v>
+        <v>0.3643</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1029</v>
+        <v>0.2268</v>
       </c>
       <c r="V3" t="n">
         <v>1.1403</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8494</v>
+        <v>2.6678</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9242</v>
+        <v>1.9408</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9252</v>
+        <v>0.727</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5586</v>
@@ -766,13 +766,13 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4372</v>
+        <v>1.2556</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5324</v>
+        <v>0.4842</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9697</v>
+        <v>0.7715</v>
       </c>
       <c r="V4" t="n">
         <v>0.5047</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7346</v>
+        <v>2.3343</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2578</v>
+        <v>1.5602</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4768</v>
+        <v>0.7741</v>
       </c>
       <c r="G5" t="n">
         <v>-2.8506</v>
@@ -844,13 +844,13 @@
         <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4436</v>
+        <v>0.1561</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.46</v>
+        <v>-0.1576</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0164</v>
+        <v>0.3137</v>
       </c>
       <c r="V5" t="n">
         <v>4.1125</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. CASASUS GOYENECHE</t>
+          <t>F. FERRER I SEGURA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.306</v>
+        <v>1.6007</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0177</v>
+        <v>2.0709</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3237</v>
+        <v>-0.4702</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5861</v>
+        <v>2.4391</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2208</v>
+        <v>1.2369</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3652</v>
+        <v>1.2022</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6444</v>
+        <v>3.2041</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1057</v>
+        <v>1.7773</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7501</v>
+        <v>1.4268</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0584</v>
+        <v>-0.765</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3265</v>
+        <v>-0.5404</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3849</v>
+        <v>-0.2246</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3665</v>
+        <v>0.3665</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4661</v>
+        <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2152</v>
+        <v>0.3758</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1705</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0448</v>
+        <v>0.2811</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1288</v>
+        <v>-1.5806</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1288</v>
+        <v>-1.2691</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. FERRER I SEGURA</t>
+          <t>G. CASASUS GOYENECHE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6445</v>
+        <v>1.3317</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0404</v>
+        <v>-0.3884</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3959</v>
+        <v>1.7201</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4391</v>
+        <v>0.5861</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2369</v>
+        <v>0.2208</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2022</v>
+        <v>0.3652</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2041</v>
+        <v>0.6444</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7773</v>
+        <v>-0.1057</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4268</v>
+        <v>0.7501</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.765</v>
+        <v>-0.0584</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5404</v>
+        <v>0.3265</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2246</v>
+        <v>-0.3849</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3665</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5805</v>
+        <v>1.241</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9359</v>
+        <v>0.7998</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3554</v>
+        <v>0.4412</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.5806</v>
+        <v>-0.1288</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2691</v>
+        <v>-0.1288</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.366</v>
+        <v>0.6264</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5585</v>
+        <v>1.1905</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1925</v>
+        <v>-0.5641</v>
       </c>
       <c r="G8" t="n">
         <v>1.4219</v>
@@ -1078,13 +1078,13 @@
         <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9996</v>
+        <v>1.26</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0536</v>
+        <v>0.6855</v>
       </c>
       <c r="U8" t="n">
-        <v>0.946</v>
+        <v>0.5744</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7727000000000001</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.044</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1047</v>
+        <v>0.3906</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0607</v>
+        <v>-1.1351</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8249</v>
@@ -1156,13 +1156,13 @@
         <v>1.6493</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3245</v>
+        <v>0.536</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2074</v>
+        <v>0.4932</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1171</v>
+        <v>0.0428</v>
       </c>
       <c r="V9" t="n">
         <v>0.6439</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.273</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2951</v>
+        <v>-1.8581</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0221</v>
+        <v>0.923</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6966</v>
@@ -1234,13 +1234,13 @@
         <v>0.733</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9309</v>
+        <v>1.2689</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3726</v>
+        <v>0.8096</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5584</v>
+        <v>0.4593</v>
       </c>
       <c r="V10" t="n">
         <v>-0.324</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7835</v>
+        <v>-2.7041</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.209</v>
+        <v>-3.9066</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4255</v>
+        <v>1.2026</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1959</v>
@@ -1312,13 +1312,13 @@
         <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3287</v>
+        <v>0.4082</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2949</v>
+        <v>0.0076</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6236</v>
+        <v>0.4006</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.2972</v>
+        <v>13.1231</v>
       </c>
       <c r="E12" t="n">
-        <v>8.423700000000002</v>
+        <v>9.249400000000001</v>
       </c>
       <c r="F12" t="n">
         <v>3.8736</v>
@@ -1390,10 +1390,10 @@
         <v>16.4933</v>
       </c>
       <c r="S12" t="n">
-        <v>7.6958</v>
+        <v>8.522</v>
       </c>
       <c r="T12" t="n">
-        <v>3.646500000000001</v>
+        <v>4.4723</v>
       </c>
       <c r="U12" t="n">
         <v>4.0496</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4237</v>
+        <v>4.5547</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7949</v>
+        <v>5.3718</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3712</v>
+        <v>-0.8172</v>
       </c>
       <c r="G13" t="n">
         <v>4.3976</v>
@@ -1468,13 +1468,13 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3508</v>
+        <v>-0.2198</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.193</v>
+        <v>-0.6161</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.3963</v>
       </c>
       <c r="V13" t="n">
         <v>0.0104</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4091</v>
+        <v>2.1925</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7281</v>
+        <v>5.623</v>
       </c>
       <c r="F14" t="n">
-        <v>0.681</v>
+        <v>-3.4305</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9733000000000001</v>
+        <v>4.7299</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6263</v>
+        <v>0.2002</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.5996</v>
+        <v>4.5298</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2576</v>
+        <v>6.8186</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7027</v>
+        <v>1.0062</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.4452</v>
+        <v>5.8124</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2309</v>
+        <v>-2.0887</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0765</v>
+        <v>-0.806</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1544</v>
+        <v>-1.2827</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1991</v>
+        <v>2.3823</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.84</v>
+        <v>-1.1182</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2413</v>
+        <v>-0.6301</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5987</v>
+        <v>-0.4881</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8559</v>
+        <v>-1.969</v>
       </c>
       <c r="W14" t="n">
-        <v>2.5444</v>
+        <v>1.267</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3115</v>
+        <v>-3.236</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0692</v>
+        <v>1.447</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9499</v>
+        <v>0.4396</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.8807</v>
+        <v>1.0074</v>
       </c>
       <c r="G15" t="n">
-        <v>4.7299</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2002</v>
+        <v>2.6263</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5298</v>
+        <v>-3.5996</v>
       </c>
       <c r="J15" t="n">
-        <v>6.8186</v>
+        <v>0.2576</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0062</v>
+        <v>2.7027</v>
       </c>
       <c r="L15" t="n">
-        <v>5.8124</v>
+        <v>-2.4452</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0887</v>
+        <v>-1.2309</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.806</v>
+        <v>-0.0765</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2827</v>
+        <v>-1.1544</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3823</v>
+        <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2415</v>
+        <v>-0.802</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3031</v>
+        <v>-0.5298</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9384</v>
+        <v>-0.2723</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.969</v>
+        <v>2.8559</v>
       </c>
       <c r="W15" t="n">
-        <v>1.267</v>
+        <v>2.5444</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.236</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0177</v>
+        <v>1.2377</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5404</v>
+        <v>1.6365</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-0.3988</v>
       </c>
       <c r="G16" t="n">
         <v>2.4012</v>
@@ -1702,13 +1702,13 @@
         <v>0.5498</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.017</v>
+        <v>-0.7969000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5324</v>
+        <v>-0.4363</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4846</v>
+        <v>-0.3607</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4035</v>
+        <v>0.0684</v>
       </c>
       <c r="E18" t="n">
-        <v>1.648</v>
+        <v>1.2634</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2445</v>
+        <v>-1.195</v>
       </c>
       <c r="G18" t="n">
         <v>0.9414</v>
@@ -1858,13 +1858,13 @@
         <v>0.1833</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.2108</v>
       </c>
       <c r="T18" t="n">
-        <v>0.586</v>
+        <v>0.2014</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0401</v>
+        <v>0.0094</v>
       </c>
       <c r="V18" t="n">
         <v>-1.267</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.766</v>
+        <v>-0.9554</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.905</v>
+        <v>-1.1935</v>
       </c>
       <c r="F19" t="n">
-        <v>0.139</v>
+        <v>0.2381</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2795</v>
@@ -1936,13 +1936,13 @@
         <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3374</v>
+        <v>-0.5268</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1637</v>
+        <v>-0.1248</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5011</v>
+        <v>-0.402</v>
       </c>
       <c r="V19" t="n">
         <v>0.3011</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0247</v>
+        <v>-2.8314</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.013</v>
+        <v>-2.6604</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0117</v>
+        <v>-0.171</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1326</v>
+        <v>-1.5568</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1146</v>
+        <v>1.793</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2472</v>
+        <v>-3.3499</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2408</v>
+        <v>-0.1016</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9162</v>
+        <v>2.2541</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.157</v>
+        <v>-2.3557</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8919</v>
+        <v>-1.4552</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1983</v>
+        <v>-0.4611</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0902</v>
+        <v>-0.9941</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8326</v>
+        <v>2.1991</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6419</v>
+        <v>-0.9391</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0604</v>
+        <v>-0.7262</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4185</v>
+        <v>-0.2129</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.5339</v>
+        <v>-0.702</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.5339</v>
+        <v>-0.702</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>I. EGIDO MUNOZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3632</v>
+        <v>-3.9352</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2373</v>
+        <v>-2.6657</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1258</v>
+        <v>-1.2695</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5568</v>
+        <v>-0.6551</v>
       </c>
       <c r="H21" t="n">
-        <v>1.793</v>
+        <v>-0.8762</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.3499</v>
+        <v>0.2211</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1016</v>
+        <v>0.125</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2541</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.3557</v>
+        <v>0.125</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4552</v>
+        <v>-0.7801</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4611</v>
+        <v>-0.8762</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9941</v>
+        <v>0.0961</v>
       </c>
       <c r="P21" t="n">
+        <v>-2.3823</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-2.7489</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.3665</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.8326</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.1991</v>
-      </c>
       <c r="S21" t="n">
-        <v>-1.4708</v>
+        <v>-0.5177</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3031</v>
+        <v>-0.0418</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1677</v>
+        <v>-0.4759</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.702</v>
+        <v>-0.3801</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.702</v>
+        <v>-0.3801</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4356</v>
+        <v>-3.9556</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0568</v>
+        <v>-2.1668</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6212</v>
+        <v>-1.7888</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8192</v>
+        <v>-1.1326</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1524</v>
+        <v>1.1146</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-2.2472</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.6388</v>
+        <v>-0.2408</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5235</v>
+        <v>0.9162</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1154</v>
+        <v>-1.157</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1804</v>
+        <v>-0.8919</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.629</v>
+        <v>0.1983</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4486</v>
+        <v>-1.0902</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.0995</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6493</v>
+        <v>1.8326</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1471</v>
+        <v>-0.289</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0015</v>
+        <v>-0.0935</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1457</v>
+        <v>-0.1955</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3697</v>
+        <v>-2.5339</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3324</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.702</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>I. EGIDO MUNOZ</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.451</v>
+        <v>-4.0665</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9541</v>
+        <v>-4.3453</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4968</v>
+        <v>0.2787</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6551</v>
+        <v>-1.8192</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8762</v>
+        <v>-1.1524</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2211</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.125</v>
+        <v>-1.6388</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-0.5235</v>
       </c>
       <c r="L23" t="n">
-        <v>0.125</v>
+        <v>-1.1154</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7801</v>
+        <v>-0.1804</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8762</v>
+        <v>-0.629</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0961</v>
+        <v>0.4486</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.3823</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.7489</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0335</v>
+        <v>-0.7781</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3303</v>
+        <v>-0.29</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7032</v>
+        <v>-0.4881</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3801</v>
+        <v>-0.3697</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.3324</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3801</v>
+        <v>-0.702</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.5553</v>
+        <v>-6.3877</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.344</v>
+        <v>-6.1517</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2113</v>
+        <v>-0.236</v>
       </c>
       <c r="G24" t="n">
         <v>-3.74</v>
@@ -2326,13 +2326,13 @@
         <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4456</v>
+        <v>-1.2781</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9547</v>
+        <v>-0.7624</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4909</v>
+        <v>-0.5157</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0032</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.2973</v>
+        <v>-11.6562</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.873599999999999</v>
+        <v>-3.873799999999997</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.423499999999999</v>
+        <v>-7.7826</v>
       </c>
       <c r="G25" t="n">
-        <v>2.288899999999999</v>
+        <v>2.288899999999998</v>
       </c>
       <c r="H25" t="n">
         <v>6.456299999999996</v>
@@ -2377,7 +2377,7 @@
         <v>-4.167300000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>9.336900000000002</v>
+        <v>9.3369</v>
       </c>
       <c r="K25" t="n">
         <v>8.853400000000001</v>
@@ -2386,7 +2386,7 @@
         <v>0.4833000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.0485</v>
+        <v>-7.048499999999999</v>
       </c>
       <c r="N25" t="n">
         <v>-2.3975</v>
@@ -2404,16 +2404,16 @@
         <v>14.6607</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.695899999999999</v>
+        <v>-7.0549</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.049300000000001</v>
+        <v>-4.0496</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.6467</v>
+        <v>-3.0055</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.057499999999999</v>
+        <v>-5.057500000000001</v>
       </c>
       <c r="W25" t="n">
         <v>7.332100000000001</v>
